--- a/Esquema BD.xlsx
+++ b/Esquema BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\InvestigaApi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B5B49C-6F02-43E2-A230-1ED88D925E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D393FB9-83A0-4A02-A4C8-675A61C46E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{396E9530-9DAA-4C80-9BE3-0374E9017F87}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>Alquileres</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Id_Estado</t>
   </si>
   <si>
-    <t>Id_condicion</t>
-  </si>
-  <si>
     <t>CondicionPago</t>
   </si>
   <si>
@@ -83,18 +80,12 @@
     <t>EstadoAlquileres</t>
   </si>
   <si>
-    <t>Id_estado</t>
-  </si>
-  <si>
     <t>Estado</t>
   </si>
   <si>
     <t>Usuarios</t>
   </si>
   <si>
-    <t>Id_usuario</t>
-  </si>
-  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -107,9 +98,6 @@
     <t>Auditoria</t>
   </si>
   <si>
-    <t>Id_auditoria</t>
-  </si>
-  <si>
     <t>Accion</t>
   </si>
   <si>
@@ -119,13 +107,16 @@
     <t>FechaHora</t>
   </si>
   <si>
-    <t>Inquilinos</t>
-  </si>
-  <si>
-    <t>Apellidos</t>
-  </si>
-  <si>
-    <t>Id_inquilino</t>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Nombre_Inquilino</t>
+  </si>
+  <si>
+    <t>Id_Categoria</t>
+  </si>
+  <si>
+    <t>Id_Auditoria</t>
   </si>
 </sst>
 </file>
@@ -155,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -178,15 +169,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -208,71 +209,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>809580</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>132600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>49035</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>165120</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="5" name="Entrada de lápiz 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEA3B3DC-A669-0529-5E6E-B9AC3BB25E14}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="3286080" y="2037600"/>
-            <a:ext cx="811080" cy="794520"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="5" name="Entrada de lápiz 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEA3B3DC-A669-0529-5E6E-B9AC3BB25E14}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3279960" y="2031480"/>
-              <a:ext cx="823320" cy="806760"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>619080</xdr:colOff>
       <xdr:row>18</xdr:row>
@@ -284,9 +220,9 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>9600</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Entrada de lápiz 5">
               <a:extLst>
@@ -304,7 +240,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Entrada de lápiz 5">
@@ -349,8 +285,8 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>154920</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="7" name="Entrada de lápiz 6">
@@ -369,7 +305,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="7" name="Entrada de lápiz 6">
@@ -414,8 +350,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>144180</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Entrada de lápiz 7">
@@ -434,7 +370,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Entrada de lápiz 7">
@@ -479,8 +415,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>118320</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="9" name="Entrada de lápiz 8">
@@ -499,7 +435,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="9" name="Entrada de lápiz 8">
@@ -534,24 +470,24 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>285075</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>122820</xdr:rowOff>
+      <xdr:colOff>47475</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>126600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>742995</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>135540</xdr:rowOff>
+      <xdr:colOff>741915</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>117120</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="10" name="Entrada de lápiz 9">
+            <xdr14:cNvPr id="2" name="Entrada de lápiz 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D59CFD2-F259-60DB-9D6E-7CE38989AAAC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD590BAA-3F17-F8B6-AFFB-AB89D5EBEE63}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -559,18 +495,18 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="3571200" y="3361320"/>
-            <a:ext cx="457920" cy="774720"/>
+            <a:off x="3333600" y="1650600"/>
+            <a:ext cx="694440" cy="1514520"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
       <mc:Fallback>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="10" name="Entrada de lápiz 9">
+            <xdr:cNvPr id="2" name="Entrada de lápiz 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D59CFD2-F259-60DB-9D6E-7CE38989AAAC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD590BAA-3F17-F8B6-AFFB-AB89D5EBEE63}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -584,8 +520,138 @@
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3565080" y="3355200"/>
-              <a:ext cx="470160" cy="786960"/>
+              <a:off x="3327480" y="1644480"/>
+              <a:ext cx="706680" cy="1526760"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>295035</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171180</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>295395</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171540</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="3" name="Entrada de lápiz 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5040359A-8A4E-7A32-C5F5-FF25F24D0E6E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="6248160" y="3028680"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="3" name="Entrada de lápiz 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5040359A-8A4E-7A32-C5F5-FF25F24D0E6E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6242040" y="3022560"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>37875</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>63060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>747795</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95340</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="4" name="Entrada de lápiz 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2504C91-01C7-7D4C-1624-9207F7517872}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5229000" y="3301560"/>
+            <a:ext cx="709920" cy="413280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="Entrada de lápiz 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2504C91-01C7-7D4C-1624-9207F7517872}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5222880" y="3295440"/>
+              <a:ext cx="722160" cy="425520"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -615,33 +681,6 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-03-07T15:23:37.489"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 2 24575,'50'0'0,"7"-1"0,0 2 0,98 15 0,-125-10 0,1 1 0,46 18 0,-57-18 0,0-1 0,0 0 0,0-2 0,1-1 0,31 2 0,110-7 0,-60-1 0,-79 2 0,-14 1 0,0-1 0,1 1 0,-1 1 0,0 0 0,13 3 0,-19-4 0,-1 1 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,-1-1 0,1 1 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,0 0 0,-1 0 0,1 1 0,0-1 0,0 4 0,2 24 0,-1 0 0,-2 0 0,-4 42 0,1 7 0,3-4 0,2-37 0,-2 0 0,-2-1 0,-1 1 0,-2-1 0,-14 56 0,-2-4 0,17-64 0,-1-1 0,-14 39 0,11-41 0,1 1 0,1 0 0,1 1 0,1-1 0,-1 36 0,6 125 0,3-73 0,-4 201 0,-2-293 0,0 0 0,-1-1 0,-1 1 0,0-1 0,-9 19 0,7-17 0,0 1 0,1-1 0,-5 39 0,8-34 0,-2 1 0,-12 41 0,-2 7 0,18-72 0,0 0 0,-1-1 0,1 1 0,0 0 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,-1 1 0,1-1 0,2 0 0,9 1 0,1 0 0,0-1 0,-1 0 0,17-3 0,-6 1 0,5 0 0,1-1 0,-1-1 0,0-2 0,43-13 0,-46 11 0,0 2 0,1 1 0,0 1 0,31 0 0,114 6 0,-61 1 0,-26-2 0,96-3 0,-110-10 0,-51 7 0,0 1 0,28-1 0,193 6 0,-699-1 0,601 0-1365,-113 0-5461</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
       <inkml:timestamp xml:id="ts0" timeString="2026-03-07T15:23:38.717"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
@@ -653,7 +692,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -680,7 +719,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -707,7 +746,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -734,6 +773,33 @@
 </inkml:ink>
 </file>
 
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-07T15:53:24.173"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 19 24575,'0'-1'0,"1"-1"0,-1 1 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,1 0 0,-1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,1 0 0,-1-1 0,0 1 0,1 0 0,-1 0 0,0 0 0,3 0 0,40 0 0,-28 4 0,-1 0 0,1 1 0,-1 1 0,21 11 0,-23-11 0,0 0 0,0 0 0,0-1 0,1-1 0,0-1 0,23 4 0,9-4 0,0-3 0,0-2 0,0-1 0,-1-3 0,62-15 0,-106 20 0,0 1 0,0-1 0,0 1 0,0 0 0,1 0 0,-1-1 0,0 1 0,0 0 0,0 0 0,1 0 0,-1 1 0,0-1 0,0 0 0,0 0 0,0 0 0,1 1 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,0 0 0,1 1 0,0 0 0,-1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,1-1 0,-1 0 0,-1 3 0,0 9 0,-1 1 0,0-1 0,-7 20 0,8-27 0,-75 242 0,11-37 0,23-86 0,-7 24 0,27-61 0,3 1 0,4 0 0,4 2 0,1 92 0,9-59 0,4 118 0,24-54 0,-23-166 0,2 1 0,1-1 0,14 36 0,-12-37 0,-1 0 0,-1 0 0,-1 0 0,4 29 0,-6 255 0,-7-155 0,3 1189 0,-1-1328 0,0 0 0,-1 0 0,0 0 0,-5 15 0,-2 7 0,9-33 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1 0 0,1 0 0,0-1 0,0 1 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,2-1 0,53 0 0,-45 0 0,13-1 0,-1-1 0,1-2 0,-1 0 0,-1-1 0,32-14 0,-36 15 0,-1 1 0,1 0 0,32-1 0,-33 3 0,0 0 0,0 0 0,1-2 0,17-6 0,3-4 0,0 2 0,0 1 0,1 2 0,46-4 0,-59 9 0,0-2 0,0 0 0,45-18 0,22-6 0,-74 26 0,1 1 0,-1 0 0,1 1 0,0 1 0,0 1 0,0 1 0,0 1 0,0 1 0,-1 0 0,1 1 0,-1 1 0,0 1 0,0 1 0,-1 1 0,21 11 0,-30-14 9,1-1 0,0 0 0,1-1 0,-1 0-1,1 0 1,-1-1 0,1 0 0,0-1 0,21-1 0,36 6-1463,-45-1-5372</inkml:trace>
+</inkml:ink>
+</file>
+
 <file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -750,14 +816,41 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-03-07T15:24:54.525"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-07T15:53:31.703"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1272 3 24575,'-138'-3'0,"-148"7"0,274-2 0,1 0 0,-1 1 0,1 0 0,0 1 0,-15 7 0,15-6 0,-1 0 0,0-1 0,0 0 0,-17 3 0,-54-3 0,64-4 0,1 0 0,0 1 0,-1 1 0,-32 9 0,9 0 0,-1-1 0,0-2 0,-47 3 0,87-11 0,0 1 0,-1-1 0,1 1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0 0 0,1 0 0,-1 0 0,1 1 0,-3 3 0,0-1 0,1 1 0,1 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,-2 11 0,-1 10 0,1 0 0,2 0 0,-1 31 0,3-44 0,-28 379 0,24-349 0,-18 71 0,-3 20 0,21-102 0,-15 48 0,13-56 0,1 0 0,0 1 0,-2 46 0,-5 66 0,0 9 0,14 314 0,-2-455 0,1-1 0,0 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,1 0 0,-1 0 0,1 0 0,1 0 0,3 7 0,-3-9 0,-1 0 0,1-1 0,0 1 0,0-1 0,0 0 0,1 0 0,-1 0 0,0 0 0,1-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,-1 0 0,1 0 0,0-1 0,0 0 0,5 0 0,34 0 0,0-1 0,-1-3 0,47-9 0,-46 6 0,62-8 0,186-4 0,-288 20 0,17 0 0,0-1 0,-1-1 0,1 0 0,0-1 0,-1-2 0,1 0 0,29-10 0,-22 6-45,-1 1 1,1 1-1,1 1 0,-1 2 0,0 1 0,1 1 0,41 4 1,-17-2-963,-29-1-5819</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'0'0'-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-07T15:55:30.306"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1148 24575,'16'0'0,"1"0"0,-1-2 0,0 0 0,1-1 0,-1 0 0,0-1 0,0-1 0,-1 0 0,0-2 0,0 1 0,0-2 0,0 0 0,16-13 0,44-36 0,-2-3 0,111-122 0,-144 143 0,-27 28 0,-1 0 0,-1-1 0,0 0 0,0-1 0,-2 0 0,1-1 0,-2 0 0,0 0 0,7-17 0,41-97 0,-34 81 0,24-70 0,-8 26 0,-29 75 0,-2-1 0,1 0 0,-2-1 0,0 1 0,4-28 0,-9 25 0,5-18 0,-6 37 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,1 1 0,-1-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,0 0 0,3 0 0,183 4 0,-34 1 0,-124-3 0,0 0 0,31 8 0,-29-4 0,57 2 0,-38-5 41,0 2 0,56 14 1,-55-9-787,98 6 1,-121-16-6082</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1078,43 +1171,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309F1F61-6FE6-400B-97FC-90484644AAC0}">
-  <dimension ref="D2:J21"/>
+  <dimension ref="D2:J20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="4:10" x14ac:dyDescent="0.25">
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="4:10" x14ac:dyDescent="0.25">
       <c r="F4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="4:10" x14ac:dyDescent="0.25">
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="4:10" x14ac:dyDescent="0.25">
       <c r="H6" s="3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="4:10" x14ac:dyDescent="0.25">
@@ -1122,116 +1216,117 @@
         <v>3</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D9" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D10" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D11" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D11" s="4"/>
       <c r="F11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="13" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="14" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="15" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="16" spans="4:10" x14ac:dyDescent="0.25">
       <c r="F16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F19" s="1" t="s">
+    <row r="18" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F21" t="s">
+    <row r="20" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F20" s="3" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Esquema BD.xlsx
+++ b/Esquema BD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\InvestigaApi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D393FB9-83A0-4A02-A4C8-675A61C46E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF55463B-4039-4411-AC66-A1451CF649AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{396E9530-9DAA-4C80-9BE3-0374E9017F87}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Alquileres</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>Id_Auditoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rol </t>
+  </si>
+  <si>
+    <t>Lista de opciones</t>
   </si>
 </sst>
 </file>
@@ -480,8 +486,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>117120</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Entrada de lápiz 1">
@@ -500,7 +506,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Entrada de lápiz 1">
@@ -545,8 +551,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>171540</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Entrada de lápiz 2">
@@ -565,7 +571,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Entrada de lápiz 2">
@@ -610,8 +616,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>95340</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Entrada de lápiz 3">
@@ -630,7 +636,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Entrada de lápiz 3">
@@ -1171,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309F1F61-6FE6-400B-97FC-90484644AAC0}">
-  <dimension ref="D2:J20"/>
+  <dimension ref="D2:M20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1180,22 +1186,22 @@
     <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:13" x14ac:dyDescent="0.25">
       <c r="H5" s="2" t="s">
         <v>15</v>
       </c>
@@ -1203,7 +1209,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:13" x14ac:dyDescent="0.25">
       <c r="H6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1211,7 +1217,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:13" x14ac:dyDescent="0.25">
       <c r="H7" s="3" t="s">
         <v>3</v>
       </c>
@@ -1219,7 +1225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1233,7 +1239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
@@ -1246,8 +1252,14 @@
       <c r="J9" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
@@ -1261,7 +1273,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D11" s="4"/>
       <c r="F11" s="3" t="s">
         <v>24</v>
@@ -1270,27 +1282,27 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F13" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F15" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F16" s="3" t="s">
         <v>7</v>
       </c>
